--- a/evaluation_forms/038_evaluation_service_request_form--evaluation_forms.xlsx
+++ b/evaluation_forms/038_evaluation_service_request_form--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -528,10 +528,14 @@
           <t>Business Name</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Provide your business name and contact information.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -551,10 +555,14 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Enter your email address.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -574,10 +582,14 @@
           <t>Phone Number</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter your phone number.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +606,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Description of Service Request</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please describe the service you are requesting.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,125 +633,149 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Select One</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Preferred Time of Day</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Select your preferred time of day for the evaluation.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Preferred Date and Time</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Select your preferred date and time for the evaluation.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>assigned_tool</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Assigned Tool</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Specify the tool(s) to be used during the evaluation.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select the category of the evaluation.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Select Multiple Locations</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select multiple locations for the evaluation.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Additional Notes</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please provide any additional comments or notes.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>repeat_category</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Repeat Category</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Another category for evaluation.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -773,15 +817,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>more_repeat_category</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>More Repeat Category</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Yet another category for evaluation.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -796,15 +844,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>another_repeat_category</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Another Repeat Category</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Another category for evaluation.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -819,131 +871,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>last_repeat_category</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Last Repeat Category</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>The last category for evaluation.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -960,12 +901,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +934,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>hawaii</t>
+          <t>08:00_am_-_10:00_am</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hawaii</t>
+          <t>08:00 AM - 10:00 AM</t>
         </is>
       </c>
     </row>
@@ -1010,12 +951,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>oahu</t>
+          <t>10:00_am_-_12:00_pm</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Oahu</t>
+          <t>10:00 AM - 12:00 PM</t>
         </is>
       </c>
     </row>
@@ -1027,12 +968,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>maui</t>
+          <t>12:00_pm_-_02:00_pm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Maui</t>
+          <t>12:00 PM - 02:00 PM</t>
         </is>
       </c>
     </row>
@@ -1044,80 +985,165 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>kona</t>
+          <t>02:00_pm_-_04:00_pm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kona</t>
+          <t>02:00 PM - 04:00 PM</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hawaii</t>
+          <t>04:00_pm_-_06:00_pm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hawaii</t>
+          <t>04:00 PM - 06:00 PM</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>oahu</t>
+          <t>06:00_pm_-_08:00_pm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oahu</t>
+          <t>06:00 PM - 08:00 PM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>maui</t>
+          <t>08:00_pm_-_10:00_pm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Maui</t>
+          <t>08:00 PM - 10:00 PM</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>category_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>category_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>safety</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>category_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>select_multiple_choices</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>kona</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Kona</t>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>location_1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Location 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>select_multiple_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>location_2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Location 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>select_multiple_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>location_3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Location 3</t>
         </is>
       </c>
     </row>
